--- a/template/SPA/country_data.xlsx
+++ b/template/SPA/country_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://paho-my.sharepoint.com/personal/caine_paho_org/Documents/WDC/Polio/2024/AR municipal/polio-risk-assessment-main/template/SPA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5aee5c5b004427f/Documents/polio-risk-assessment/template/SPA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{7ED16B22-7A80-4343-BA43-63BFC975C1AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{782F7CCB-5660-4C4D-BB9F-21C0A0A59AEE}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{7ED16B22-7A80-4343-BA43-63BFC975C1AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19655512-A01D-4B5C-A8AF-C0262004FC38}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{7CFA64C4-648F-B840-901A-EC2D94882293}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CFA64C4-648F-B840-901A-EC2D94882293}"/>
   </bookViews>
   <sheets>
     <sheet name="1-General" sheetId="1" r:id="rId1"/>
@@ -1116,10 +1116,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
